--- a/01_Reporting_Suite/Data_Baseplan/BASEPLAN_CHARGES.xlsx
+++ b/01_Reporting_Suite/Data_Baseplan/BASEPLAN_CHARGES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coateshire-my.sharepoint.com/personal/andrew_fisher_coateshire_com_au/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coateshire-my.sharepoint.com/personal/andrew_fisher_coateshire_com_au/Documents/Desktop/Cement/01_Reporting_Suite/Data_Baseplan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B20CDB-3852-4703-AFB8-5B5DEB1C79A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{F4CEE05E-A900-4480-9E95-57D9AC3BE8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6956EA76-C72F-4BC8-A008-DCDFE35F8D65}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{103A9CC0-28F9-4E57-AD9A-272A13CBBC04}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FAB16066-971A-423C-8A73-4696DBE4D1B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="133">
   <si>
     <t>Line</t>
   </si>
@@ -417,6 +417,27 @@
   </si>
   <si>
     <t>016/000</t>
+  </si>
+  <si>
+    <t>SUB-2284</t>
+  </si>
+  <si>
+    <t>Welder - Motorised - Diesel - 500A Air Vantage C/W A/Comp</t>
+  </si>
+  <si>
+    <t>017/000</t>
+  </si>
+  <si>
+    <t>PUMPOUT</t>
+  </si>
+  <si>
+    <t>Pumpout Service - Pumpout of toilet 122447 3/8/26</t>
+  </si>
+  <si>
+    <t>GLST-TOI</t>
+  </si>
+  <si>
+    <t>018/000</t>
   </si>
 </sst>
 </file>
@@ -794,17 +815,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD0610E-059E-4457-918C-55D8B4B57B3A}">
-  <dimension ref="A1:BR17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D8ABEC-FE66-49D2-829F-7B13764B32B9}">
+  <dimension ref="A1:BR19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="6" max="6" width="44.5546875" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
-    <col min="25" max="25" width="15.109375" customWidth="1"/>
-    <col min="26" max="26" width="15.21875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1041,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>24210.9</v>
+        <v>3586.8</v>
       </c>
       <c r="J2" s="1">
         <v>12.81</v>
@@ -1076,6 +1089,12 @@
       <c r="Z2" s="3">
         <v>0.29166666666666669</v>
       </c>
+      <c r="AC2" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE2" s="1">
         <v>0</v>
       </c>
@@ -1083,13 +1102,13 @@
         <v>0</v>
       </c>
       <c r="AG2" s="1">
-        <v>0</v>
+        <v>13450.5</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI2" s="1">
-        <v>0</v>
+        <v>14795.55</v>
       </c>
       <c r="AM2">
         <v>0</v>
@@ -1154,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>17850</v>
+        <v>3570</v>
       </c>
       <c r="J3" s="1">
         <v>29.75</v>
@@ -1189,6 +1208,12 @@
       <c r="Z3" s="3">
         <v>0.29166666666666669</v>
       </c>
+      <c r="AC3" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE3" s="1">
         <v>0</v>
       </c>
@@ -1196,13 +1221,13 @@
         <v>0</v>
       </c>
       <c r="AG3" s="1">
-        <v>0</v>
+        <v>7140</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI3" s="1">
-        <v>0</v>
+        <v>7854</v>
       </c>
       <c r="AM3">
         <v>0</v>
@@ -1267,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>10452.959999999999</v>
+        <v>1742.16</v>
       </c>
       <c r="J4" s="1">
         <v>72.59</v>
@@ -1302,6 +1327,12 @@
       <c r="Z4" s="3">
         <v>0.29166666666666669</v>
       </c>
+      <c r="AC4" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE4" s="1">
         <v>0</v>
       </c>
@@ -1309,13 +1340,13 @@
         <v>0</v>
       </c>
       <c r="AG4" s="1">
-        <v>0</v>
+        <v>5226.4799999999996</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI4" s="1">
-        <v>0</v>
+        <v>5749.13</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1380,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>1742.16</v>
+        <v>290.36</v>
       </c>
       <c r="J5" s="1">
         <v>72.59</v>
@@ -1415,6 +1446,12 @@
       <c r="Z5" s="3">
         <v>0.29166666666666669</v>
       </c>
+      <c r="AC5" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE5" s="1">
         <v>0</v>
       </c>
@@ -1422,13 +1459,13 @@
         <v>0</v>
       </c>
       <c r="AG5" s="1">
-        <v>0</v>
+        <v>871.08</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI5" s="1">
-        <v>0</v>
+        <v>958.19</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1493,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>88.62</v>
+        <v>8.44</v>
       </c>
       <c r="J6" s="1">
         <v>2.11</v>
@@ -1525,6 +1562,12 @@
       <c r="Z6" s="3">
         <v>0.51249999999999996</v>
       </c>
+      <c r="AC6" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE6" s="1">
         <v>0</v>
       </c>
@@ -1532,13 +1575,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="1">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI6" s="1">
-        <v>0</v>
+        <v>23.21</v>
       </c>
       <c r="AM6">
         <v>0</v>
@@ -1606,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>88.62</v>
+        <v>8.44</v>
       </c>
       <c r="J7" s="1">
         <v>2.11</v>
@@ -1638,6 +1681,12 @@
       <c r="Z7" s="3">
         <v>0.51249999999999996</v>
       </c>
+      <c r="AC7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE7" s="1">
         <v>0</v>
       </c>
@@ -1645,13 +1694,13 @@
         <v>0</v>
       </c>
       <c r="AG7" s="1">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI7" s="1">
-        <v>0</v>
+        <v>23.21</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1719,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>88.4</v>
+        <v>176.8</v>
       </c>
       <c r="J8" s="1">
         <v>44.2</v>
@@ -1754,6 +1803,12 @@
       <c r="Z8" s="3">
         <v>0.51249999999999996</v>
       </c>
+      <c r="AC8" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE8" s="1">
         <v>0</v>
       </c>
@@ -1761,13 +1816,13 @@
         <v>0</v>
       </c>
       <c r="AG8" s="1">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI8" s="1">
-        <v>0</v>
+        <v>486.2</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1832,7 +1887,7 @@
         <v>5.5</v>
       </c>
       <c r="I9" s="1">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="V9" t="s">
         <v>100</v>
@@ -1843,6 +1898,12 @@
       <c r="Z9" s="3">
         <v>0.51388888888888884</v>
       </c>
+      <c r="AC9" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>0.83472222222222225</v>
+      </c>
       <c r="AE9" s="1">
         <v>0</v>
       </c>
@@ -1850,13 +1911,13 @@
         <v>0</v>
       </c>
       <c r="AG9" s="1">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AI9" s="1">
-        <v>0</v>
+        <v>302.5</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1909,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>20.16</v>
+        <v>1.92</v>
       </c>
       <c r="J10" s="1">
         <v>0.16</v>
@@ -1941,6 +2002,12 @@
       <c r="Z10" s="3">
         <v>0.42638888888888887</v>
       </c>
+      <c r="AC10" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE10" s="1">
         <v>0</v>
       </c>
@@ -1948,13 +2015,13 @@
         <v>0</v>
       </c>
       <c r="AG10" s="1">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI10" s="1">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -2019,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>42.84</v>
+        <v>4.08</v>
       </c>
       <c r="J11" s="1">
         <v>0.17</v>
@@ -2051,6 +2118,12 @@
       <c r="Z11" s="3">
         <v>0.42638888888888887</v>
       </c>
+      <c r="AC11" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE11" s="1">
         <v>0</v>
       </c>
@@ -2058,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="AG11" s="1">
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI11" s="1">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -2129,7 +2202,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="V12" t="s">
         <v>110</v>
@@ -2140,6 +2213,12 @@
       <c r="Z12" s="3">
         <v>0.42777777777777776</v>
       </c>
+      <c r="AC12" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0.83472222222222225</v>
+      </c>
       <c r="AE12" s="1">
         <v>0</v>
       </c>
@@ -2147,13 +2226,13 @@
         <v>0</v>
       </c>
       <c r="AG12" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AI12" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2206,7 +2285,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="V13" t="s">
         <v>110</v>
@@ -2217,6 +2296,12 @@
       <c r="Z13" s="3">
         <v>0.42777777777777776</v>
       </c>
+      <c r="AC13" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0.83472222222222225</v>
+      </c>
       <c r="AE13" s="1">
         <v>0</v>
       </c>
@@ -2224,13 +2309,13 @@
         <v>0</v>
       </c>
       <c r="AG13" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AI13" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2283,7 +2368,7 @@
         <v>190</v>
       </c>
       <c r="I14" s="1">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>110</v>
@@ -2294,6 +2379,12 @@
       <c r="Z14" s="3">
         <v>0.57152777777777775</v>
       </c>
+      <c r="AC14" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0.83472222222222225</v>
+      </c>
       <c r="AE14" s="1">
         <v>0</v>
       </c>
@@ -2301,13 +2392,13 @@
         <v>0</v>
       </c>
       <c r="AG14" s="1">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AI14" s="1">
-        <v>0</v>
+        <v>313.5</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2360,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>2720</v>
+        <v>640</v>
       </c>
       <c r="J15" s="1">
         <v>160</v>
@@ -2395,6 +2486,12 @@
       <c r="Z15" s="3">
         <v>0.37847222222222221</v>
       </c>
+      <c r="AC15" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE15" s="1">
         <v>0</v>
       </c>
@@ -2402,13 +2499,13 @@
         <v>0</v>
       </c>
       <c r="AG15" s="1">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI15" s="1">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2473,7 +2570,7 @@
         <v>190</v>
       </c>
       <c r="I16" s="1">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="V16" t="s">
         <v>110</v>
@@ -2484,6 +2581,12 @@
       <c r="Z16" s="3">
         <v>0.38055555555555554</v>
       </c>
+      <c r="AC16" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0.83472222222222225</v>
+      </c>
       <c r="AE16" s="1">
         <v>0</v>
       </c>
@@ -2491,13 +2594,13 @@
         <v>0</v>
       </c>
       <c r="AG16" s="1">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AI16" s="1">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2550,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>564</v>
+        <v>1290</v>
       </c>
       <c r="J17" s="1">
         <v>564</v>
@@ -2585,6 +2688,12 @@
       <c r="Z17" s="3">
         <v>0.29166666666666669</v>
       </c>
+      <c r="AC17" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AE17" s="1">
         <v>0</v>
       </c>
@@ -2592,13 +2701,13 @@
         <v>0</v>
       </c>
       <c r="AG17" s="1">
-        <v>0</v>
+        <v>1692</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="1">
-        <v>0</v>
+        <v>1861.2</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2638,6 +2747,196 @@
       </c>
       <c r="BL17" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1161.44</v>
+      </c>
+      <c r="J18" s="1">
+        <v>72.59</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>46246</v>
+      </c>
+      <c r="U18">
+        <v>7</v>
+      </c>
+      <c r="V18" t="s">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>46223</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>25999830</v>
+      </c>
+      <c r="AT18" s="2">
+        <v>46223</v>
+      </c>
+      <c r="AU18" s="2">
+        <v>46246</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>127754</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>76</v>
+      </c>
+      <c r="BJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>190</v>
+      </c>
+      <c r="I19" s="1">
+        <v>190</v>
+      </c>
+      <c r="V19" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>46238</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0.40763888888888888</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>25999897</v>
+      </c>
+      <c r="AT19" s="2">
+        <v>46217</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
